--- a/data/trans_bre/P1802_2016_2023-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1802_2016_2023-Edad-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>4,82</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 8,87</t>
+          <t>-0,02; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 10,04</t>
+          <t>-1,97; 10,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 110,3</t>
+          <t>-0,97; 111,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 244,12</t>
+          <t>-23,91; 210,11</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,83%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 7,79</t>
+          <t>-0,24; 7,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 4,56</t>
+          <t>-2,93; 5,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 79,87</t>
+          <t>-2,06; 83,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,51; 57,76</t>
+          <t>-24,3; 81,11</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,88</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-15,87%</t>
+          <t>-6,4%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,12</t>
+          <t>-1,98; 5,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 1,22</t>
+          <t>-4,66; 2,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 50,36</t>
+          <t>-12,7; 48,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 8,05</t>
+          <t>-25,63; 21,84</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-19,4</t>
+          <t>5,49</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-48,8%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 3,59</t>
+          <t>-4,67; 3,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 4,67</t>
+          <t>1,95; 8,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 24,49</t>
+          <t>-25,02; 25,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-74,2; 29,76</t>
+          <t>10,53; 65,26</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,86</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 15,55</t>
+          <t>4,61; 15,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 8,88</t>
+          <t>1,37; 9,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,88; 118,88</t>
+          <t>24,9; 119,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 46,19</t>
+          <t>6,08; 52,45</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-4,78</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-25,29%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 14,36</t>
+          <t>1,78; 14,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 4,05</t>
+          <t>-1,06; 7,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,51; 103,16</t>
+          <t>8,71; 104,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-71,57; 22,98</t>
+          <t>-5,16; 45,38</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>4,99</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 12,2</t>
+          <t>-1,15; 12,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 8,56</t>
+          <t>0,54; 8,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 82,28</t>
+          <t>-5,76; 78,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 65,56</t>
+          <t>3,59; 69,63</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-21,43%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,2</t>
+          <t>2,75; 6,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 2,08</t>
+          <t>1,89; 5,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,14; 46,19</t>
+          <t>17,93; 47,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 13,29</t>
+          <t>11,53; 37,62</t>
         </is>
       </c>
     </row>
